--- a/public/assets/data/projects.xlsx
+++ b/public/assets/data/projects.xlsx
@@ -1,179 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ragha\OneDrive\Documents\Raghav Personal\My Projects\portfolio\public\assets\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E942BF0-A443-4D0B-903E-130CDC5A0EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>tech</t>
-  </si>
-  <si>
-    <t>github</t>
-  </si>
-  <si>
-    <t>demo</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>progress</t>
-  </si>
-  <si>
-    <t>featured</t>
-  </si>
-  <si>
-    <t>Jarvis</t>
-  </si>
-  <si>
-    <t>A desktop voice / text assistant that listens to commands and performs tasks like opening apps, fetching data, etc.</t>
-  </si>
-  <si>
-    <t>Python, Eel, HTML, JavaScript</t>
-  </si>
-  <si>
-    <t>https://github.com/RaghavSethi006/jarvis</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Bank Management System</t>
-  </si>
-  <si>
-    <t>A system to manage bank operations including account creation, fund transfers, and transaction tracking.</t>
-  </si>
-  <si>
-    <t>https://github.com/RaghavSethi006/bank-management-system</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>RAG-based Chatbot for Embedded Data</t>
-  </si>
-  <si>
-    <t>A chatbot using Retrieval-Augmented Generation (RAG) that retrieves domain-specific embedding data and responds accordingly.</t>
-  </si>
-  <si>
-    <t>https://github.com/RaghavSethi006/RAG-based-chatbot-for-custom-data-embedding</t>
-  </si>
-  <si>
-    <t>Face Recognition Attendance System</t>
-  </si>
-  <si>
-    <t>Attendance system that uses face recognition (via camera) to mark presence/absence automatically.</t>
-  </si>
-  <si>
-    <t>https://github.com/RaghavSethi006/Face-Recognition-attendance-system-</t>
-  </si>
-  <si>
-    <t>Wi-Fi Password Extractor</t>
-  </si>
-  <si>
-    <t>A tool to extract saved Wi-Fi passwords from the system.</t>
-  </si>
-  <si>
-    <t>(specify language)</t>
-  </si>
-  <si>
-    <t>https://github.com/RaghavSethi006/Wi-Fi-password-extractor-</t>
-  </si>
-  <si>
-    <t>Travel Data Analysis App</t>
-  </si>
-  <si>
-    <t>App for analyzing travel-related data (e.g. trends, patterns, visualizations).</t>
-  </si>
-  <si>
-    <t>(your stack, e.g. Python, JS, D3, Pandas)</t>
-  </si>
-  <si>
-    <t>https://github.com/RaghavSethi006/Travel-data-analysis-app</t>
-  </si>
-  <si>
-    <t>Clock Frontend Practice</t>
-  </si>
-  <si>
-    <t>A frontend exercise / component: a clock (analog or digital) as a UI piece.</t>
-  </si>
-  <si>
-    <t>(React / Vanilla JS / CSS)</t>
-  </si>
-  <si>
-    <t>https://github.com/RaghavSethi006/Clock-frontend-practice</t>
-  </si>
-  <si>
-    <t>Rivalry Chess</t>
-  </si>
-  <si>
-    <t>A chess game / platform or UI for playing chess (possibly with opponent support).</t>
-  </si>
-  <si>
-    <t>(JS / game engine / backend stack)</t>
-  </si>
-  <si>
-    <t>https://github.github.com/RaghavSethi006/Rivalry-chess-</t>
-  </si>
-  <si>
-    <t>Smart Desk</t>
-  </si>
-  <si>
-    <t>A “smart desk” project (automated / IoT / interactive desk) — details in repository.</t>
-  </si>
-  <si>
-    <t>(whatever hardware / software stack)</t>
-  </si>
-  <si>
-    <t>https://github.com/RaghavSethi006/Smart-Desk</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>(Python, LangChain, embeddings, vector DB)</t>
-  </si>
-  <si>
-    <t>(Python, OpenCV, face-recognition)</t>
-  </si>
-  <si>
-    <t>(Python , CSV, tkinter)</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -203,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -542,284 +396,400 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="37.09765625" customWidth="1"/>
-    <col min="3" max="3" width="111.796875" customWidth="1"/>
-    <col min="4" max="4" width="55.09765625" customWidth="1"/>
-    <col min="5" max="5" width="73.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.09765625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K14"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>description</v>
+      </c>
+      <c r="D1" t="str">
+        <v>tech</v>
+      </c>
+      <c r="E1" t="str">
+        <v>github</v>
+      </c>
+      <c r="F1" t="str">
+        <v>demo</v>
+      </c>
+      <c r="G1" t="str">
+        <v>status</v>
+      </c>
+      <c r="H1" t="str">
+        <v>progress</v>
+      </c>
+      <c r="I1" t="str">
+        <v>featured</v>
+      </c>
+      <c r="J1" t="str">
+        <v>caseStudy</v>
+      </c>
+      <c r="K1" t="str">
+        <v>category</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
+      <c r="B2" t="str">
+        <v>Jarvis</v>
+      </c>
+      <c r="C2" t="str">
+        <v>A local-first, multi-agent AI desktop assistant with persistent four-tier memory, runtime self-synthesis, neural voice, biometric auth, and a British butler attitude.</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Python, React, Groq, ChromaDB, Kokoro TTS, OpenCV, MediaPipe, SQLite, asyncio</v>
+      </c>
+      <c r="E2" t="str">
+        <v>https://github.com/RaghavSethi006/jarvis</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Completed</v>
       </c>
       <c r="H2">
         <v>100</v>
       </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I2" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
+      <c r="B3" t="str">
+        <v>Career Co-Pilot</v>
+      </c>
+      <c r="C3" t="str">
+        <v>An AI-powered career intelligence system that optimizes job applications for quality over volume — with RAG-powered resume tailoring, visible browser submission, and feedback learning loops.</v>
+      </c>
+      <c r="D3" t="str">
+        <v>React, TypeScript, FastAPI, Python, Gemini AI, Playwright, SQLite, Docker, Zustand</v>
+      </c>
+      <c r="E3" t="str">
+        <v>https://github.com/RaghavSethi006/Career-Co-Pilot</v>
+      </c>
+      <c r="G3" t="str">
+        <v>In Progress</v>
       </c>
       <c r="H3">
-        <v>100</v>
-      </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
+      <c r="B4" t="str">
+        <v>TaskArena v2</v>
+      </c>
+      <c r="C4" t="str">
+        <v>A personal AI study companion — manage tasks, index notes with SciBERT, chat with an AI grounded in your own lecture slides, generate quizzes, and build smarter schedules.</v>
+      </c>
+      <c r="D4" t="str">
+        <v>React, TypeScript, Tauri v2, FastAPI, SQLAlchemy, SciBERT, Zustand, Vite, SQLite</v>
+      </c>
+      <c r="E4" t="str">
+        <v>https://github.com/RaghavSethi006/TaskArena2.0</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Completed</v>
       </c>
       <c r="H4">
         <v>100</v>
       </c>
-      <c r="I4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I4" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
+      <c r="B5" t="str">
+        <v>FinOS</v>
+      </c>
+      <c r="C5" t="str">
+        <v>A local-first, privacy-first Financial Operating System — combining finance tracking, double-entry accounting, investment portfolio, encrypted document vault, and tax assistant in one desktop app.</v>
+      </c>
+      <c r="D5" t="str">
+        <v>React, TypeScript, Tauri v2, SQLite, Zustand, Recharts, AES-256-GCM, Zod, Tailwind CSS</v>
+      </c>
+      <c r="E5" t="str">
+        <v>https://github.com/RaghavSethi006/FinOS</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Completed</v>
       </c>
       <c r="H5">
         <v>100</v>
       </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I5" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
+      <c r="B6" t="str">
+        <v>Schema Spark</v>
+      </c>
+      <c r="C6" t="str">
+        <v>An enterprise-grade visual ER modeling platform that treats relationships as first-class citizens and generates production-ready backend code across FastAPI, Django, NestJS, Express, and Spring Boot.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>React, TypeScript, React Flow, Zustand, Zod, JSZip, Tailwind CSS, Vite, shadcn/ui</v>
+      </c>
+      <c r="E6" t="str">
+        <v>https://github.com/RaghavSethi006/schema-spark</v>
+      </c>
+      <c r="F6" t="str">
+        <v>https://schema-spark-sigma.vercel.app/</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Completed</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
-      <c r="I6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I6" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
+      <c r="B7" t="str">
+        <v>multi-style</v>
+      </c>
+      <c r="C7" t="str">
+        <v>A cross-framework UI component playground — customize components visually and export production-ready code for React, Angular, Streamlit, tkinter, or WinUI3.</v>
+      </c>
+      <c r="D7" t="str">
+        <v>React, TypeScript, Tailwind CSS, Zustand, Vite, shadcn/ui, Radix UI</v>
+      </c>
+      <c r="E7" t="str">
+        <v>https://github.com/RaghavSethi006/multi-style</v>
+      </c>
+      <c r="F7" t="str">
+        <v>https://multi-style.vercel.app/</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Completed</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
-      <c r="I7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I7" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
+      <c r="B8" t="str">
+        <v>RageBait-AI</v>
+      </c>
+      <c r="C8" t="str">
+        <v>A high-intensity cognitive reaction engine with AI-powered real-time trash-talk via Gemini, Firestore leaderboards, and progressive accessibility including a comprehensive Blind Mode.</v>
+      </c>
+      <c r="D8" t="str">
+        <v>React, Vite, Gemini 2.0 Flash, Firebase Firestore, Vercel Functions, Tailwind CSS, Framer Motion, Zod</v>
+      </c>
+      <c r="E8" t="str">
+        <v>https://github.com/RaghavSethi006/RageBait-AI</v>
+      </c>
+      <c r="F8" t="str">
+        <v>https://rage-bait-ai-mpx6.vercel.app/</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Completed</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
-      <c r="I8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I8" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
+      <c r="B9" t="str">
+        <v>Local Eco</v>
+      </c>
+      <c r="C9" t="str">
+        <v>A decentralized, cloudless Discord clone using WebRTC DataChannels — star topology with host migration, E2E encryption via ECDH + AES-256-GCM, and direct-routed DMs.</v>
+      </c>
+      <c r="D9" t="str">
+        <v>React, TypeScript, WebRTC, Web Crypto API, Tailwind CSS, shadcn/ui, Vite</v>
+      </c>
+      <c r="E9" t="str">
+        <v>https://github.com/RaghavSethi006/local-echo</v>
+      </c>
+      <c r="F9" t="str">
+        <v>https://off-grid-networking.vercel.app/</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Completed</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
-      <c r="I9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I9" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" t="s">
-        <v>45</v>
+      <c r="B10" t="str">
+        <v>Face Recognition Attendance</v>
+      </c>
+      <c r="C10" t="str">
+        <v>A Tkinter-based desktop application using OpenCV LBPH face recognition and SQLite to capture faces, train a recognizer, and mark attendance automatically with timestamps.</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Python, OpenCV, SQLite3, Tkinter, Pandas, Pillow</v>
+      </c>
+      <c r="E10" t="str">
+        <v>https://github.com/RaghavSethi006/Face-Recognition-attendance-system-</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Completed</v>
       </c>
       <c r="H10">
-        <v>60</v>
-      </c>
-      <c r="I10" t="s">
-        <v>18</v>
+        <v>100</v>
+      </c>
+      <c r="I10" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Open Photos</v>
+      </c>
+      <c r="C11" t="str">
+        <v>A privacy-focused, self-hosted desktop photo manager that brings Google Photos-style browsing, face recognition, duplicate cleanup, albums, and map-based discovery to your local machine.</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Tauri v2, Rust, React 19, TypeScript, Tailwind CSS 4, Zustand, ONNX, InsightFace, Leaflet, EXIF, JSON storage</v>
+      </c>
+      <c r="E11" t="str">
+        <v>https://github.com/yourusername/local-google-photos</v>
+      </c>
+      <c r="G11" t="str">
+        <v>In Progress</v>
+      </c>
+      <c r="H11">
+        <v>85</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Desktop Application</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>ZenOS</v>
+      </c>
+      <c r="C12" t="str">
+        <v>A focus shell for your desktop — pick a profile, and for the length of a session your desktop becomes just a timer, an allow-listed browser, a scoped file explorer, and whatever apps you said you needed. Everything else waits outside.</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Tauri 2, Rust, React, TypeScript, Zustand, Vite</v>
+      </c>
+      <c r="E12" t="str">
+        <v>https://github.com/RaghavSethi006/zenos</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="H12">
+        <v>100</v>
+      </c>
+      <c r="I12" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Targets</v>
+      </c>
+      <c r="C13" t="str">
+        <v>A habit tracker, calendar, and to-do list unified into one app — everything you track is a Target with a smart recurrence rule, powered by a React Native frontend and a FastAPI recurrence engine.</v>
+      </c>
+      <c r="D13" t="str">
+        <v>React Native, Expo, TypeScript, FastAPI, Python, SQLite, Zustand</v>
+      </c>
+      <c r="G13" t="str">
+        <v>In Progress</v>
+      </c>
+      <c r="H13">
+        <v>70</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>FitPulse</v>
+      </c>
+      <c r="C14" t="str">
+        <v>An AI-powered native Android fitness and nutrition ecosystem featuring multimodal Gemini food plate vision scanning, 2D biomechanical workout guides with voice coaching, and local Room persistence.</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Kotlin, Jetpack Compose, Android SDK, Gemini AI, Room SQLite, Material 3, Coroutines, Retrofit</v>
+      </c>
+      <c r="E14" t="str">
+        <v>https://github.com/RaghavSethi006/Fitpulse-</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="H14">
+        <v>100</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Mobile &amp; AI Systems</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:I2 B1:I1 A6:I10 A4:C4 E4:I4 A5:C5 E5:I5 A3:C3 E3:I3" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K14"/>
   </ignoredErrors>
 </worksheet>
 </file>